--- a/HSI_FSC_result/4. C Way/score_15way.xlsx
+++ b/HSI_FSC_result/4. C Way/score_15way.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_4_15way\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\4. C Way\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5DF4F0-5C08-445C-9F1F-EBB9202BC271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4C7E96-3FDB-4A87-9065-9853114716FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7935" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -79,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -358,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>38.333331999999999</v>
       </c>
@@ -396,7 +403,7 @@
         <v>31.3068718</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>55.323196000000003</v>
       </c>
@@ -432,7 +439,7 @@
         <v>50.006545799999998</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>37.77619</v>
       </c>
@@ -468,7 +475,7 @@
         <v>33.023336199999996</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>61.307899999999997</v>
       </c>
@@ -504,7 +511,7 @@
         <v>47.036864899999998</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>27.628150000000002</v>
       </c>
@@ -540,7 +547,7 @@
         <v>53.175433600000005</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>98.679869999999994</v>
       </c>
@@ -576,7 +583,7 @@
         <v>81.154581000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>13.023255000000001</v>
       </c>
@@ -612,7 +619,7 @@
         <v>37.547734900000002</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>80.61224</v>
       </c>
@@ -648,7 +655,7 @@
         <v>85.282166899999993</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>30.303032000000002</v>
       </c>
@@ -684,7 +691,7 @@
         <v>20.5471781</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>44.927536000000003</v>
       </c>
@@ -720,7 +727,7 @@
         <v>44.966260800000001</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>74.188484000000003</v>
       </c>
@@ -756,7 +763,7 @@
         <v>63.078564599999993</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>70.438800000000001</v>
       </c>
@@ -792,7 +799,7 @@
         <v>45.273327500000001</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>45.253864</v>
       </c>
@@ -828,7 +835,7 @@
         <v>52.825399400000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>77.845529999999997</v>
       </c>
@@ -864,7 +871,7 @@
         <v>86.802233799999996</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>95.652175999999997</v>
       </c>
@@ -900,7 +907,7 @@
         <v>52.3080474</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>86.666663999999997</v>
       </c>
@@ -936,7 +943,7 @@
         <v>52.588762599999995</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>57.849546297199701</v>
       </c>
@@ -972,7 +979,7 @@
         <v>54.267733437408467</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>58.622515201568604</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>52.307707071304286</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>53.008957655241602</v>
       </c>
@@ -1045,6 +1052,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1053,10 +1061,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="1">
         <v>98.020780000000002</v>
       </c>
       <c r="B1">
@@ -1091,8 +1099,8 @@
         <v>93.73830199999999</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
         <v>99.718630000000005</v>
       </c>
       <c r="B2">
@@ -1127,8 +1135,8 @@
         <v>94.416898200000006</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>96.081419999999994</v>
       </c>
       <c r="B3">
@@ -1163,8 +1171,8 @@
         <v>88.494856200000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>87.783370000000005</v>
       </c>
       <c r="B4">
@@ -1199,8 +1207,8 @@
         <v>93.197434400000006</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>97.698419999999999</v>
       </c>
       <c r="B5">
@@ -1235,8 +1243,8 @@
         <v>96.8934426</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>99.539990000000003</v>
       </c>
       <c r="B6">
@@ -1271,8 +1279,8 @@
         <v>94.5317024</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>94.376980000000003</v>
       </c>
       <c r="B7">
@@ -1307,8 +1315,8 @@
         <v>94.818748800000009</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>82.706764000000007</v>
       </c>
       <c r="B8">
@@ -1343,8 +1351,8 @@
         <v>86.442357900000019</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>90.862430000000003</v>
       </c>
       <c r="B9">
@@ -1379,8 +1387,8 @@
         <v>97.83554460000002</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>98.338486000000003</v>
       </c>
       <c r="B10">
@@ -1415,8 +1423,8 @@
         <v>91.1249076</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>98.684209999999993</v>
       </c>
       <c r="B11">
@@ -1451,8 +1459,8 @@
         <v>90.415742000000009</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>98.686369999999997</v>
       </c>
       <c r="B12">
@@ -1487,8 +1495,8 @@
         <v>95.112889600000003</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>90.863950000000003</v>
       </c>
       <c r="B13">
@@ -1523,8 +1531,8 @@
         <v>89.206283899999988</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>92.68929</v>
       </c>
       <c r="B14">
@@ -1559,8 +1567,8 @@
         <v>87.745611900000014</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>68.018020000000007</v>
       </c>
       <c r="B15">
@@ -1595,8 +1603,8 @@
         <v>63.34005659999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>99.882000000000005</v>
       </c>
       <c r="B16">
@@ -1631,8 +1639,8 @@
         <v>87.392120000000006</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>89.122281956067894</v>
       </c>
       <c r="B17">
@@ -1667,8 +1675,8 @@
         <v>86.209979862920051</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>93.371945619583101</v>
       </c>
       <c r="B18">
@@ -1703,8 +1711,8 @@
         <v>90.294181704521122</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>87.891339466434403</v>
       </c>
       <c r="B19">
@@ -1740,6 +1748,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1748,9 +1757,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>85.2089</v>
       </c>
@@ -1786,7 +1795,7 @@
         <v>88.478082600000008</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>89.329459999999997</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>91.705781999999985</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>61.036312000000002</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>60.374143800000013</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>87.368769999999998</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>73.862521799999982</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>88.428664999999995</v>
       </c>
@@ -1930,7 +1939,7 @@
         <v>91.815873100000005</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>37.249040000000001</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>40.727742399999997</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>51.250613999999999</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>48.929550399999997</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>82.03125</v>
       </c>
@@ -2038,7 +2047,7 @@
         <v>75.901419000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>75.341030000000003</v>
       </c>
@@ -2074,7 +2083,7 @@
         <v>72.161901700000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>75.689639049934499</v>
       </c>
@@ -2110,7 +2119,7 @@
         <v>73.121610248737582</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>73.027110099792395</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>71.550779342651339</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>68.655710453177605</v>
       </c>
@@ -2183,6 +2192,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2190,8 +2200,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2199,8 +2210,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>